--- a/artfynd/A 3689-2026 artfynd.xlsx
+++ b/artfynd/A 3689-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104387920</v>
+        <v>137229396</v>
       </c>
       <c r="B5" t="n">
-        <v>96426</v>
+        <v>96703</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,35 +1046,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jätteask S om Hagalund, Hakarp, Jönköping, Sm</t>
+          <t>Död jätteask S om Hagalund, Hakarp, Jönköping, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460035</v>
+        <v>460034</v>
       </c>
       <c r="R5" t="n">
-        <v>6406161</v>
+        <v>6406162</v>
       </c>
       <c r="S5" t="n">
         <v>14</v>
@@ -1101,27 +1110,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Längre upp på asken stam</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,6 +1136,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1147,16 +1171,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104387920</t>
+          <t>https://artportalen.se/Sighting/137229396</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>813031</v>
+        <v>104387920</v>
       </c>
       <c r="B6" t="n">
-        <v>96183</v>
+        <v>96426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,37 +1188,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2674</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten baronmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomodon longifolius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schleich. ex Brid.) Hartm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jätteask (07E1c28), Sm</t>
+          <t>Jätteask S om Hagalund, Hakarp, Jönköping, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460021</v>
+        <v>460035</v>
       </c>
       <c r="R6" t="n">
-        <v>6406169</v>
+        <v>6406161</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,17 +1243,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2002-02-07</t>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2002-02-07</t>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>070412281 / ANOM LON / Allmän-riklig (3)  / OBJ.AREA:0 ha</t>
+          <t>Längre upp på asken stam</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,40 +1274,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Grova ädellövträd /</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Uno Björkman</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
-        </is>
-      </c>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/813031</t>
+          <t>https://artportalen.se/Sighting/104387920</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117354739</v>
+        <v>137229404</v>
       </c>
       <c r="B7" t="n">
-        <v>96183</v>
+        <v>96692</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,24 +1306,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2674</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten baronmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomodon longifolius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schleich. ex Brid.) Hartm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>utan kapsel</t>
@@ -1305,14 +1336,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jätteask S om Hagalund, Hakarp, Jönköping, Sm</t>
+          <t>Död jätteask S om Hagalund, Hakarp, Jönköping, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460035</v>
+        <v>460034</v>
       </c>
       <c r="R7" t="n">
-        <v>6406161</v>
+        <v>6406162</v>
       </c>
       <c r="S7" t="n">
         <v>14</v>
@@ -1339,22 +1370,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,12 +1409,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Fraxinus excelsior</t>
+          <t>Bark of dead wood # Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1400,16 +1431,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117354739</t>
+          <t>https://artportalen.se/Sighting/137229404</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117354757</v>
+        <v>813031</v>
       </c>
       <c r="B8" t="n">
-        <v>96231</v>
+        <v>96183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,42 +1448,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2779</v>
+        <v>2674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Liten baronmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Anomodon longifolius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Schleich. ex Brid.) Hartm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jätteask S om Hagalund, Hakarp, Jönköping, Sm</t>
+          <t>Jätteask (07E1c28), Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460035</v>
+        <v>460021</v>
       </c>
       <c r="R8" t="n">
-        <v>6406161</v>
+        <v>6406169</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,22 +1502,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2002-02-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2002-02-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>070412281 / ANOM LON / Allmän-riklig (3)  / OBJ.AREA:0 ha</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,50 +1524,39 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Fraxinus excelsior</t>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>William Rosén</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Uno Björkman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117354757</t>
+          <t>https://artportalen.se/Sighting/813031</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>108908547</v>
+        <v>117354739</v>
       </c>
       <c r="B9" t="n">
-        <v>107609</v>
+        <v>96183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,31 +1564,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219686</v>
+        <v>2674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Liten baronmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Anomodon longifolius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schleich. ex Brid.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1617,22 +1623,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,6 +1649,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1658,58 +1684,64 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108908547</t>
+          <t>https://artportalen.se/Sighting/117354739</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>83517609</v>
+        <v>137229412</v>
       </c>
       <c r="B10" t="n">
-        <v>106813</v>
+        <v>96449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>2674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Liten baronmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Anomodon longifolius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Schleich. ex Brid.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gunnestorp, Sm</t>
+          <t>Död jätteask S om Hagalund, Hakarp, Jönköping, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460030</v>
+        <v>460034</v>
       </c>
       <c r="R10" t="n">
         <v>6406162</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1731,24 +1763,24 @@
           <t>Hakarp</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4B735ED2-7947-4B66-9BF0-34F8F1D9657E</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2009-08-12</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2009-08-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Kan ha varit hamlat för länge sedan.</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,35 +1791,51 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Gustafsson, Nisse Lennartsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83517609</t>
+          <t>https://artportalen.se/Sighting/137229412</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5005247</v>
+        <v>117354757</v>
       </c>
       <c r="B11" t="n">
-        <v>101326</v>
+        <v>96231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,37 +1843,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>2779</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jätteask (07E1c28), Sm</t>
+          <t>Jätteask S om Hagalund, Hakarp, Jönköping, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460021</v>
+        <v>460035</v>
       </c>
       <c r="R11" t="n">
-        <v>6406169</v>
+        <v>6406161</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1849,17 +1902,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2002-02-07</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2002-02-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>070412281 / HEPA NOB / Tämligen allmän (2)  / OBJ.AREA:0 ha</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,77 +1929,97 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Grova ädellövträd /</t>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Uno Björkman</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
-        </is>
-      </c>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5005247</t>
+          <t>https://artportalen.se/Sighting/117354757</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6691992</v>
+        <v>108908547</v>
       </c>
       <c r="B12" t="n">
-        <v>80477</v>
+        <v>107609</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229504</v>
+        <v>219686</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Jätteask (07E1c28), Sm</t>
+          <t>Jätteask S om Hagalund, Hakarp, Jönköping, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460021</v>
+        <v>460035</v>
       </c>
       <c r="R12" t="n">
-        <v>6406169</v>
+        <v>6406161</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1965,17 +2043,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2002-02-07</t>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2002-02-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>070412281 / PEL COLL / Enstaka-sparsam (1)  / OBJ.AREA:0 ha</t>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,92 +2069,73 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grova ädellövträd /</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Uno Björkman</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
-        </is>
-      </c>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6691992</t>
+          <t>https://artportalen.se/Sighting/108908547</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103605662</v>
+        <v>83517609</v>
       </c>
       <c r="B13" t="n">
-        <v>80477</v>
+        <v>106813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229504</v>
+        <v>220785</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Jätteask S om Hagalund, Hakarp, Jönköping, Sm</t>
+          <t>Gunnestorp, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460035</v>
+        <v>460030</v>
       </c>
       <c r="R13" t="n">
-        <v>6406161</v>
+        <v>6406162</v>
       </c>
       <c r="S13" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2093,29 +2157,24 @@
           <t>Hakarp</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4B735ED2-7947-4B66-9BF0-34F8F1D9657E</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:49</t>
+          <t>2009-08-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:49</t>
+          <t>2009-08-12</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Asken är mycket gammal, och hamlad i äldre tid. Dessvärre tycks den, vid första anblick, ha insjuknat i askskottssjuka, och varit omvuxen av gran och hassel under en längre tid.</t>
+          <t>Kan ha varit hamlat för länge sedan.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2130,16 +2189,514 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson, Nisse Lennartsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83517609</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137229293</v>
+      </c>
+      <c r="B14" t="n">
+        <v>107100</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Död jätteask S om Hagalund, Hakarp, Jönköping, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>460034</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6406162</v>
+      </c>
+      <c r="S14" t="n">
+        <v>14</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hakarp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Trädet var drabbat av askskottssjuka och slutade få nya blad för ett par år sedan. Nu faller trädet långsamt ihop och är genomvuxen av klubbhonungsskivling.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>William Rosén</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>William Rosén</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr">
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137229293</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5005247</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jätteask (07E1c28), Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>460021</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6406169</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hakarp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2002-02-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2002-02-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>070412281 / HEPA NOB / Tämligen allmän (2)  / OBJ.AREA:0 ha</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Uno Björkman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5005247</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6691992</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jätteask (07E1c28), Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>460021</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6406169</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hakarp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2002-02-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2002-02-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>070412281 / PEL COLL / Enstaka-sparsam (1)  / OBJ.AREA:0 ha</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Grova ädellövträd /</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Uno Björkman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6691992</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>103605662</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jätteask S om Hagalund, Hakarp, Jönköping, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>460035</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6406161</v>
+      </c>
+      <c r="S17" t="n">
+        <v>14</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hakarp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Asken är mycket gammal, och hamlad i äldre tid. Dessvärre tycks den, vid första anblick, ha insjuknat i askskottssjuka, och varit omvuxen av gran och hassel under en längre tid.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/103605662</t>
         </is>
@@ -2159,6 +2716,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3689-2026 artfynd.xlsx
+++ b/artfynd/A 3689-2026 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>137229396</v>
       </c>
       <c r="B5" t="n">
-        <v>96703</v>
+        <v>96705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>137229404</v>
       </c>
       <c r="B7" t="n">
-        <v>96692</v>
+        <v>96694</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>137229412</v>
       </c>
       <c r="B10" t="n">
-        <v>96449</v>
+        <v>96451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137229293</v>
       </c>
       <c r="B14" t="n">
-        <v>107100</v>
+        <v>107102</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3689-2026 artfynd.xlsx
+++ b/artfynd/A 3689-2026 artfynd.xlsx
@@ -1069,11 +1069,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Död jätteask S om Hagalund, Hakarp, Jönköping, Sm</t>
@@ -1329,11 +1325,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Död jätteask S om Hagalund, Hakarp, Jönköping, Sm</t>
@@ -1724,11 +1716,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Död jätteask S om Hagalund, Hakarp, Jönköping, Sm</t>

--- a/artfynd/A 3689-2026 artfynd.xlsx
+++ b/artfynd/A 3689-2026 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>137229396</v>
       </c>
       <c r="B5" t="n">
-        <v>96705</v>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>137229404</v>
       </c>
       <c r="B7" t="n">
-        <v>96694</v>
+        <v>96697</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>137229412</v>
       </c>
       <c r="B10" t="n">
-        <v>96451</v>
+        <v>96454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>137229293</v>
       </c>
       <c r="B14" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3689-2026 artfynd.xlsx
+++ b/artfynd/A 3689-2026 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>137229396</v>
       </c>
       <c r="B5" t="n">
-        <v>96708</v>
+        <v>96718</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>137229404</v>
       </c>
       <c r="B7" t="n">
-        <v>96697</v>
+        <v>96707</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>137229412</v>
       </c>
       <c r="B10" t="n">
-        <v>96454</v>
+        <v>96464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>137229293</v>
       </c>
       <c r="B14" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3689-2026 artfynd.xlsx
+++ b/artfynd/A 3689-2026 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>137229396</v>
       </c>
       <c r="B5" t="n">
-        <v>96718</v>
+        <v>96719</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>137229404</v>
       </c>
       <c r="B7" t="n">
-        <v>96707</v>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>137229412</v>
       </c>
       <c r="B10" t="n">
-        <v>96464</v>
+        <v>96465</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>137229293</v>
       </c>
       <c r="B14" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3689-2026 artfynd.xlsx
+++ b/artfynd/A 3689-2026 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>137229396</v>
       </c>
       <c r="B5" t="n">
-        <v>96719</v>
+        <v>96724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>137229404</v>
       </c>
       <c r="B7" t="n">
-        <v>96708</v>
+        <v>96713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>137229412</v>
       </c>
       <c r="B10" t="n">
-        <v>96465</v>
+        <v>96470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>137229293</v>
       </c>
       <c r="B14" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3689-2026 artfynd.xlsx
+++ b/artfynd/A 3689-2026 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>137229396</v>
       </c>
       <c r="B5" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>137229404</v>
       </c>
       <c r="B7" t="n">
-        <v>96713</v>
+        <v>96715</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>137229412</v>
       </c>
       <c r="B10" t="n">
-        <v>96470</v>
+        <v>96472</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>137229293</v>
       </c>
       <c r="B14" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3689-2026 artfynd.xlsx
+++ b/artfynd/A 3689-2026 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>137229396</v>
       </c>
       <c r="B5" t="n">
-        <v>96726</v>
+        <v>96732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>137229404</v>
       </c>
       <c r="B7" t="n">
-        <v>96715</v>
+        <v>96721</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>137229412</v>
       </c>
       <c r="B10" t="n">
-        <v>96472</v>
+        <v>96478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>137229293</v>
       </c>
       <c r="B14" t="n">
-        <v>107135</v>
+        <v>107141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3689-2026 artfynd.xlsx
+++ b/artfynd/A 3689-2026 artfynd.xlsx
@@ -2201,7 +2201,7 @@
         <v>137229293</v>
       </c>
       <c r="B14" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3689-2026 artfynd.xlsx
+++ b/artfynd/A 3689-2026 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>137229396</v>
       </c>
       <c r="B5" t="n">
-        <v>96732</v>
+        <v>96744</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>137229404</v>
       </c>
       <c r="B7" t="n">
-        <v>96721</v>
+        <v>96733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>137229412</v>
       </c>
       <c r="B10" t="n">
-        <v>96478</v>
+        <v>96490</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>137229293</v>
       </c>
       <c r="B14" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3689-2026 artfynd.xlsx
+++ b/artfynd/A 3689-2026 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>137229396</v>
       </c>
       <c r="B5" t="n">
-        <v>96744</v>
+        <v>96745</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>137229404</v>
       </c>
       <c r="B7" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>137229412</v>
       </c>
       <c r="B10" t="n">
-        <v>96490</v>
+        <v>96491</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>137229293</v>
       </c>
       <c r="B14" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3689-2026 artfynd.xlsx
+++ b/artfynd/A 3689-2026 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>137229396</v>
       </c>
       <c r="B5" t="n">
-        <v>96745</v>
+        <v>96748</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>137229404</v>
       </c>
       <c r="B7" t="n">
-        <v>96734</v>
+        <v>96737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>137229412</v>
       </c>
       <c r="B10" t="n">
-        <v>96491</v>
+        <v>96494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>137229293</v>
       </c>
       <c r="B14" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3689-2026 artfynd.xlsx
+++ b/artfynd/A 3689-2026 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>137229396</v>
       </c>
       <c r="B5" t="n">
-        <v>96748</v>
+        <v>96752</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>137229404</v>
       </c>
       <c r="B7" t="n">
-        <v>96737</v>
+        <v>96741</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>137229412</v>
       </c>
       <c r="B10" t="n">
-        <v>96494</v>
+        <v>96498</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>137229293</v>
       </c>
       <c r="B14" t="n">
-        <v>107158</v>
+        <v>107164</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
